--- a/accountant-skill/data/output/Jan2026/ledger_summary_Jan2026.xlsx
+++ b/accountant-skill/data/output/Jan2026/ledger_summary_Jan2026.xlsx
@@ -116,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -136,11 +136,39 @@
     <border>
       <bottom style="double"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -182,6 +210,32 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -556,11 +610,11 @@
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -591,6 +645,8 @@
           <t>LEDGER FILES</t>
         </is>
       </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="18" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -717,34 +773,38 @@
     <row r="14"/>
     <row r="15"/>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>CONTROL ACCOUNT RECONCILIATION</t>
         </is>
       </c>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="18" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>GL Balance</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Subsidiary Total</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
@@ -759,7 +819,7 @@
       <c r="B18" s="7" t="n">
         <v>2605000</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="21" t="n">
         <v>3360000</v>
       </c>
       <c r="D18" s="8" t="n">
@@ -780,7 +840,7 @@
       <c r="B19" s="7" t="n">
         <v>1368000</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="21" t="n">
         <v>1368000</v>
       </c>
       <c r="D19" s="7" t="n">
@@ -801,7 +861,7 @@
       <c r="B20" s="7" t="n">
         <v>1438500</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="21" t="n">
         <v>1438500</v>
       </c>
       <c r="D20" s="7" t="n">
@@ -836,16 +896,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -921,7 +981,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="10" t="n">
         <v>10000</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -968,7 +1028,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="7" t="n">
         <v>10100</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -1011,7 +1071,7 @@
       <c r="K6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="10" t="n">
         <v>11000</v>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -1058,7 +1118,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="10" t="n">
         <v>12000</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -1105,7 +1165,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="7" t="n">
         <v>12200</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1148,7 +1208,7 @@
       <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="7" t="n">
         <v>12400</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -1191,7 +1251,7 @@
       <c r="K10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>13000</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -1234,7 +1294,7 @@
       <c r="K11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n">
+      <c r="A12" s="7" t="n">
         <v>15100</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -1277,7 +1337,7 @@
       <c r="K12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="7" t="n">
         <v>15110</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -1320,7 +1380,7 @@
       <c r="K13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n">
+      <c r="A14" s="7" t="n">
         <v>15200</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1363,7 +1423,7 @@
       <c r="K14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>15210</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1406,7 +1466,7 @@
       <c r="K15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n">
+      <c r="A16" s="7" t="n">
         <v>15300</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1449,7 +1509,7 @@
       <c r="K16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n">
+      <c r="A17" s="7" t="n">
         <v>15310</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1492,7 +1552,7 @@
       <c r="K17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n">
+      <c r="A18" s="10" t="n">
         <v>20000</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1539,7 +1599,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="7" t="n">
         <v>21000</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -1582,7 +1642,7 @@
       <c r="K19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
+      <c r="A20" s="7" t="n">
         <v>22200</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -1625,7 +1685,7 @@
       <c r="K20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="7" t="n">
         <v>25000</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -1668,7 +1728,7 @@
       <c r="K21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="7" t="n">
         <v>30200</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
@@ -1711,7 +1771,7 @@
       <c r="K22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="7" t="n">
         <v>31000</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1754,7 +1814,7 @@
       <c r="K23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="7" t="n">
         <v>32000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1797,7 +1857,7 @@
       <c r="K24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="7" t="n">
         <v>40000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1840,7 +1900,7 @@
       <c r="K25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="7" t="n">
         <v>50000</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1883,7 +1943,7 @@
       <c r="K26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="7" t="n">
         <v>50100</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -1926,7 +1986,7 @@
       <c r="K27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="7" t="n">
         <v>50300</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1969,7 +2029,7 @@
       <c r="K28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n">
+      <c r="A29" s="7" t="n">
         <v>50310</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -2012,7 +2072,7 @@
       <c r="K29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="7" t="n">
         <v>50320</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -2055,7 +2115,7 @@
       <c r="K30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="7" t="n">
         <v>50330</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -2098,7 +2158,7 @@
       <c r="K31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n">
+      <c r="A32" s="7" t="n">
         <v>50340</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -2141,7 +2201,7 @@
       <c r="K32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="n">
+      <c r="A33" s="7" t="n">
         <v>50350</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -2184,7 +2244,7 @@
       <c r="K33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n">
+      <c r="A34" s="7" t="n">
         <v>60000</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -2227,7 +2287,7 @@
       <c r="K34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n">
+      <c r="A35" s="7" t="n">
         <v>61000</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -2270,7 +2330,7 @@
       <c r="K35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="n">
+      <c r="A36" s="7" t="n">
         <v>62000</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -2313,7 +2373,7 @@
       <c r="K36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n">
+      <c r="A37" s="7" t="n">
         <v>63000</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -2356,7 +2416,7 @@
       <c r="K37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="n">
+      <c r="A38" s="7" t="n">
         <v>64000</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -2399,7 +2459,7 @@
       <c r="K38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="n">
+      <c r="A39" s="7" t="n">
         <v>65000</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -2442,7 +2502,7 @@
       <c r="K39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="n">
+      <c r="A40" s="7" t="n">
         <v>67000</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -2486,7 +2546,7 @@
     </row>
     <row r="41"/>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="22" t="inlineStr">
         <is>
           <t>Total Debit Balances</t>
         </is>
@@ -2495,17 +2555,17 @@
       <c r="C42" s="12" t="n"/>
       <c r="D42" s="12" t="n"/>
       <c r="E42" s="12" t="n"/>
-      <c r="F42" s="12" t="n"/>
-      <c r="G42" s="12" t="n"/>
-      <c r="H42" s="12" t="n"/>
-      <c r="I42" s="12" t="n">
+      <c r="F42" s="14" t="n"/>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="14" t="n">
         <v>20448000</v>
       </c>
       <c r="J42" s="12" t="n"/>
       <c r="K42" s="12" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>Total Credit Balances</t>
         </is>
@@ -2514,10 +2574,10 @@
       <c r="C43" s="12" t="n"/>
       <c r="D43" s="12" t="n"/>
       <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
-      <c r="H43" s="12" t="n"/>
-      <c r="I43" s="12" t="n">
+      <c r="F43" s="14" t="n"/>
+      <c r="G43" s="14" t="n"/>
+      <c r="H43" s="14" t="n"/>
+      <c r="I43" s="14" t="n">
         <v>21518000</v>
       </c>
       <c r="J43" s="12" t="n"/>
@@ -2544,12 +2604,12 @@
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2862,7 +2922,7 @@
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -2873,6 +2933,9 @@
       <c r="E20" s="14" t="n">
         <v>3360000</v>
       </c>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2895,12 +2958,12 @@
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3042,7 +3105,7 @@
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -3053,6 +3116,9 @@
       <c r="E11" s="14" t="n">
         <v>1368000</v>
       </c>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3075,12 +3141,12 @@
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3146,7 +3212,7 @@
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
@@ -3157,6 +3223,9 @@
       <c r="E7" s="14" t="n">
         <v>1438500</v>
       </c>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3181,11 +3250,11 @@
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3244,39 +3313,39 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>FA-001</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Shop 1 Building</t>
         </is>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="24" t="n">
         <v>15100</v>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="24" t="n">
         <v>3000000</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F4" s="24" t="n">
         <v>300000</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="24" t="n">
         <v>2700000</v>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Straight-Line</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -3557,14 +3626,14 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n"/>
+      <c r="B13" s="12" t="n"/>
       <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
+      <c r="D13" s="12" t="n"/>
       <c r="E13" s="14" t="n">
         <v>9300000</v>
       </c>
@@ -3574,8 +3643,8 @@
       <c r="G13" s="14" t="n">
         <v>7895500</v>
       </c>
-      <c r="H13" s="14" t="n"/>
-      <c r="I13" s="14" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3596,13 +3665,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3655,7 +3724,7 @@
       <c r="D4" s="8" t="n">
         <v>-755000</v>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>MISMATCH</t>
         </is>
@@ -3676,7 +3745,7 @@
       <c r="D5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
@@ -3697,7 +3766,7 @@
       <c r="D6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>

--- a/accountant-skill/data/output/Jan2026/ledger_summary_Jan2026.xlsx
+++ b/accountant-skill/data/output/Jan2026/ledger_summary_Jan2026.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,24 +66,15 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00FF0000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00006100"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -107,16 +98,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -136,39 +122,11 @@
     <border>
       <bottom style="double"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -189,53 +147,21 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -610,11 +536,11 @@
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -645,8 +571,6 @@
           <t>LEDGER FILES</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="18" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -672,7 +596,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -773,38 +697,34 @@
     <row r="14"/>
     <row r="15"/>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>CONTROL ACCOUNT RECONCILIATION</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="18" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>GL Balance</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Subsidiary Total</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
@@ -817,17 +737,17 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>2605000</v>
-      </c>
-      <c r="C18" s="21" t="n">
         <v>3360000</v>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>-755000</v>
+      <c r="C18" s="7" t="n">
+        <v>3360000</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>MISMATCH</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -840,7 +760,7 @@
       <c r="B19" s="7" t="n">
         <v>1368000</v>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="7" t="n">
         <v>1368000</v>
       </c>
       <c r="D19" s="7" t="n">
@@ -861,7 +781,7 @@
       <c r="B20" s="7" t="n">
         <v>1438500</v>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="7" t="n">
         <v>1438500</v>
       </c>
       <c r="D20" s="7" t="n">
@@ -892,20 +812,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -981,54 +901,54 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="8" t="n">
         <v>10000</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Cash in hand</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="9" t="n">
         <v>100000</v>
       </c>
-      <c r="H5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="10" t="n">
+      <c r="H5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9" t="n">
         <v>150000</v>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>200.0%</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>10100</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -1071,707 +991,707 @@
       <c r="K6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="8" t="n">
         <v>11000</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Account Receivable</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="9" t="n">
+        <v>800000</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>4525000</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>1965000</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>3360000</v>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>320.0%</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Inventory - Raw Material</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>450000</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>12300</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Inventory Adjustments</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n">
         <v>30000</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <v>4540000</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>1965000</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>2605000</v>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>8583.3%</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="G9" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>13000</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Advanced Payments</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Advanced Payments</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
+        <v>15100</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Buildings &amp; Structures</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Property,Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>15110</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Property,Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>15200</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Property,Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>15210</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Property,Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>450000</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>450000</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>15300</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Property,Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>800000</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>800000</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>15310</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Property,Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>160000</v>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>15400</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Electrical &amp; Utility Systems</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Property,Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>15410</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation - Electrical &amp; Utility Systems</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Property,Plant and Equipment</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Account Payables</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>798000</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>1916000</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>1368000</v>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>447.2%</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="10" t="n">
-        <v>12000</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Inventory - Raw Material</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>600000</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>450000</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>150000</v>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n">
-        <v>12200</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Inventory - Finished Goods</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>260000</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>260000</v>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>21000</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Short-term Loans</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Short-term loans</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>22200</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Wages Payable</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Accured Expenses</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>205000</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>205000</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>12400</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Work-in-Progress</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>65000</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>65000</v>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
-        <v>13000</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Advanced Payments</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Advanced Payments</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>100000</v>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
-        <v>15100</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Buildings &amp; Structures</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Property,Plant and Equipment</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="K21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>25000</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Bank Loan</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Liability</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Bank Loan</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n">
-        <v>15110</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Buildings &amp; Structures</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Property,Plant and Equipment</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
-        <v>15200</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Machinery &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Property,Plant and Equipment</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n">
-        <v>15210</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Machinery &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Property,Plant and Equipment</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>450000</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>450000</v>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>15300</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Office &amp; Facility Equipment</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Property,Plant and Equipment</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
-        <v>15310</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Accumulated Depreciation - Office &amp; Facility Equipment</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Property,Plant and Equipment</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>100000</v>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="n">
-        <v>20000</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Accounts Payable</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Account Payables</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>250000</v>
-      </c>
-      <c r="G18" s="10" t="n">
-        <v>798000</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>1916000</v>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>1368000</v>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>447.2%</t>
-        </is>
-      </c>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>21000</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Short-term Loans</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Short-term loans</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>500000</v>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>22200</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Wages Payable</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Accured Expenses</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>205000</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>205000</v>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>25000</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Bank Loan</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Liability</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Bank Loan</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>30200</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Account 30200</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="K22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="6" t="n">
         <v>31000</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
@@ -1798,23 +1718,23 @@
         <v>7180000</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="H23" s="7" t="n">
         <v>500000</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>7680000</v>
+        <v>7480000</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="6" t="n">
         <v>32000</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1857,7 +1777,7 @@
       <c r="K24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="6" t="n">
         <v>40000</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -1900,12 +1820,12 @@
       <c r="K25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
-        <v>50000</v>
+      <c r="A26" s="6" t="n">
+        <v>50110</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opening Inventory - Raw Materials </t>
+          <t>Purchases Packaging</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1927,661 +1847,489 @@
         <v>0</v>
       </c>
       <c r="G26" s="7" t="n">
+        <v>225000</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>225000</v>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
+        <v>50320</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Direct Materials Used</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Cost of Production</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="7" t="n">
         <v>2096000</v>
       </c>
-      <c r="H26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="7" t="n">
+      <c r="H27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="7" t="n">
         <v>2096000</v>
       </c>
-      <c r="J26" s="6" t="inlineStr">
+      <c r="J27" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>50100</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Opening Inventory - Packaging </t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="K27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
+        <v>53000</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Direct Labor Wages</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Cost of Production</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Production Overhead Costs</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="F27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>225000</v>
-      </c>
-      <c r="H27" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>225000</v>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
+      <c r="F28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>2755000</v>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>50300</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Opening Work-in-Progress</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="K28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
+        <v>53100</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Machine Maintenance &amp; Repair Expense</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Cost of Production</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Production Overhead Costs</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="F28" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="H28" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I28" s="7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="K28" s="6" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>50310</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Closing Work-in-Progress</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="F29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>95000</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>95000</v>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Advertising Expense</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Cost of Production</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="F29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="7" t="n">
+      <c r="F30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>62000</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Meal Allowance Expense</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>63000</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Utilities (Electricity &amp; Water)</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>125000</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>125000</v>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>64000</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Distribution Expense</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>85000</v>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
         <v>65000</v>
       </c>
-      <c r="I29" s="8" t="n">
-        <v>-65000</v>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>50320</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Direct Materials Used</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="K34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>67000</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Inventory Write-off</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Cost of Production</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="F30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>150000</v>
-      </c>
-      <c r="H30" s="7" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
+      <c r="F35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>50330</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Direct Labor Transferred to WIP</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="K35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
+        <v>68000</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Other Expenses</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Cost of Production</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>SG&amp;A</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="F31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>80000</v>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>80000</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
+      <c r="F36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>1328500</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>1328500</v>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>50340</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Manufacturing Overhead Applied</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Cost of Production</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>45000</v>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>45000</v>
-      </c>
-      <c r="I32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>50350</v>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>WIP Transferred to Finished Goods</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Cost of Production</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>260000</v>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>260000</v>
-      </c>
-      <c r="I33" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>60000</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Marketing &amp; Advertising Expense</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>SG&amp;A</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="H34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" s="6" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>61000</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Office Salaries</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>SG&amp;A</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>2755000</v>
-      </c>
-      <c r="H35" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="7" t="n">
-        <v>2755000</v>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>62000</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Meal Allowance Expense</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>SG&amp;A</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="H36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="7" t="n">
-        <v>120000</v>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="K36" s="6" t="inlineStr"/>
     </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>63000</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Utilities (Electricity &amp; Water)</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>SG&amp;A</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>125000</v>
-      </c>
-      <c r="H37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="7" t="n">
-        <v>125000</v>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K37" s="6" t="inlineStr"/>
-    </row>
+    <row r="37"/>
     <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>64000</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Distribution Expense</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>SG&amp;A</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="H38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="7" t="n">
-        <v>85000</v>
-      </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K38" s="6" t="inlineStr"/>
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Total Debit Balances</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="11" t="n"/>
+      <c r="I38" s="11" t="n">
+        <v>21493000</v>
+      </c>
+      <c r="J38" s="11" t="n"/>
+      <c r="K38" s="11" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>65000</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Factory Buildings &amp; Office Supplies and Maintenance</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>SG&amp;A</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="n">
-        <v>1468500</v>
-      </c>
-      <c r="H39" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>1468500</v>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="n">
-        <v>67000</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Inventory Write-off</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Expense</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>SG&amp;A</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K40" s="6" t="inlineStr"/>
-    </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="22" t="inlineStr">
-        <is>
-          <t>Total Debit Balances</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="12" t="n"/>
-      <c r="F42" s="14" t="n"/>
-      <c r="G42" s="14" t="n"/>
-      <c r="H42" s="14" t="n"/>
-      <c r="I42" s="14" t="n">
-        <v>20448000</v>
-      </c>
-      <c r="J42" s="12" t="n"/>
-      <c r="K42" s="12" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Total Credit Balances</t>
         </is>
       </c>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="14" t="n"/>
-      <c r="G43" s="14" t="n"/>
-      <c r="H43" s="14" t="n"/>
-      <c r="I43" s="14" t="n">
-        <v>21518000</v>
-      </c>
-      <c r="J43" s="12" t="n"/>
-      <c r="K43" s="12" t="n"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="11" t="n">
+        <v>21493000</v>
+      </c>
+      <c r="J39" s="11" t="n"/>
+      <c r="K39" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2604,12 +2352,12 @@
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2922,20 +2670,17 @@
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n">
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n">
         <v>3360000</v>
       </c>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2958,12 +2703,12 @@
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3105,20 +2850,17 @@
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n">
         <v>1368000</v>
       </c>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3141,12 +2883,12 @@
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3212,20 +2954,17 @@
     </row>
     <row r="6"/>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n">
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n">
         <v>1438500</v>
       </c>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3250,11 +2989,11 @@
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3313,39 +3052,39 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>FA-001</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Shop 1 Building</t>
         </is>
       </c>
-      <c r="C4" s="24" t="n">
+      <c r="C4" s="7" t="n">
         <v>15100</v>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="E4" s="24" t="n">
+      <c r="E4" s="7" t="n">
         <v>3000000</v>
       </c>
-      <c r="F4" s="24" t="n">
+      <c r="F4" s="7" t="n">
         <v>300000</v>
       </c>
-      <c r="G4" s="24" t="n">
+      <c r="G4" s="7" t="n">
         <v>2700000</v>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Straight-Line</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
@@ -3558,7 +3297,7 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>15300</v>
+        <v>15400</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
@@ -3597,7 +3336,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>15300</v>
+        <v>15400</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
@@ -3626,25 +3365,25 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="14" t="n">
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n">
         <v>9300000</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="13" t="n">
         <v>1404500</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="13" t="n">
         <v>7895500</v>
       </c>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3665,13 +3404,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3716,17 +3455,17 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>2605000</v>
+        <v>3360000</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>3360000</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>-755000</v>
-      </c>
-      <c r="E4" s="25" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
+      <c r="D4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3484,7 @@
       <c r="D5" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
@@ -3766,7 +3505,7 @@
       <c r="D6" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
